--- a/checksheet.xlsx
+++ b/checksheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ito\Documents\classes\Pro4\kadai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://msccnagasakiuac-my.sharepoint.com/personal/bb38124096_ms_nagasaki-u_ac_jp/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1EDABE-691C-4D29-8AE7-EA77FADECF64}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{387822FE-889E-4F07-9BB8-DB5D87FB3763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19660" windowHeight="15100" xr2:uid="{8F181CC1-B4C0-41EC-A5A7-45EF73DC96C5}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="13763" xr2:uid="{8F181CC1-B4C0-41EC-A5A7-45EF73DC96C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>設計クラス図のクラス名</t>
     <rPh sb="0" eb="2">
@@ -50,38 +50,6 @@
     <t>実装したかどうか</t>
     <rPh sb="0" eb="2">
       <t>ジッソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>y/n</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>utility.py</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>SharedLevel</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>y/nどちらかで書く</t>
-    <rPh sb="8" eb="9">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>記入例なのでこの行は削除してよい</t>
-    <rPh sb="0" eb="3">
-      <t>キニュウレイ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ギョウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>サクジョ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -106,6 +74,74 @@
     <rPh sb="8" eb="10">
       <t>キニュウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>homeScreen</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>main_screen.py</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskinputScreen</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskConfirmScreen</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskDeleteConfirmScreen</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sub_screens.py</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskStatusConfirmScreen</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CreateTaskControl</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>create_task_control.py</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Task</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>task.py</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskList</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Registration</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>User</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>main.py /task.py</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>n</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -192,9 +228,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -232,7 +268,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -338,7 +374,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -480,7 +516,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -488,27 +524,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08FF431B-DB7C-41D3-B360-5516FA9D48F4}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="32.08203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.4140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.0625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.4375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.4375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.7">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -519,7 +555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.7">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -527,10 +563,106 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.7">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.7">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.7">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.7">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.7">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.7">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.7">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.7">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.7">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -541,23 +673,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="6da8b24c-7a2d-472e-8f79-950c6996b8ef" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A647010791F03B40BD262C746FD0B2CB" ma:contentTypeVersion="18" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="be3e5f1c3b86310dba28f1b0cdd9c839">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="6da8b24c-7a2d-472e-8f79-950c6996b8ef" xmlns:ns4="7ab13428-5def-4a02-bfaf-ae2a6ae8b8a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="984a005ed9b2e6afe1bfa5a778a4dbb1" ns3:_="" ns4:_="">
     <xsd:import namespace="6da8b24c-7a2d-472e-8f79-950c6996b8ef"/>
@@ -810,32 +925,24 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="6da8b24c-7a2d-472e-8f79-950c6996b8ef" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{247799D9-DC19-4085-9FF3-400C5E8A3915}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ab13428-5def-4a02-bfaf-ae2a6ae8b8a8"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="6da8b24c-7a2d-472e-8f79-950c6996b8ef"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74FD3215-3D21-4EB1-A621-9CDB33F825D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F7D4081-1505-4883-A9F0-5D725DD92775}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -852,4 +959,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74FD3215-3D21-4EB1-A621-9CDB33F825D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{247799D9-DC19-4085-9FF3-400C5E8A3915}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ab13428-5def-4a02-bfaf-ae2a6ae8b8a8"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="6da8b24c-7a2d-472e-8f79-950c6996b8ef"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>